--- a/rater_files/rate_tables.xlsx
+++ b/rater_files/rate_tables.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seant\Desktop\RPM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seant\Desktop\GIT\PricingWorkshop_RPM2026\rater_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99D1EE9-B6C9-4F4A-9B52-03F9496465C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06070BB-A3C1-4C56-B018-00640E824CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{267F3686-BB2E-4D80-8DC1-1A87E275332A}"/>
   </bookViews>
@@ -952,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="B3">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -960,7 +960,7 @@
         <v>43</v>
       </c>
       <c r="B4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -968,7 +968,7 @@
         <v>44</v>
       </c>
       <c r="B5">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">

--- a/rater_files/rate_tables.xlsx
+++ b/rater_files/rate_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seant\Desktop\GIT\PricingWorkshop_RPM2026\rater_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06070BB-A3C1-4C56-B018-00640E824CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1816C7A-0DFC-4273-A673-11F8E20F7089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{267F3686-BB2E-4D80-8DC1-1A87E275332A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{267F3686-BB2E-4D80-8DC1-1A87E275332A}"/>
   </bookViews>
   <sheets>
     <sheet name="base_rate" sheetId="9" r:id="rId1"/>
@@ -562,17 +562,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D19C116-26DF-43CE-A321-E6EF8E780652}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>300</v>
       </c>
@@ -585,12 +585,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155B55D4-9164-4140-9F41-E50E39A105F6}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -598,7 +598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -606,7 +606,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -614,7 +614,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -622,7 +622,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -630,7 +630,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -646,7 +646,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -654,7 +654,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -662,7 +662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -670,7 +670,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -678,7 +678,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -686,7 +686,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -694,7 +694,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -702,7 +702,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -710,7 +710,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -718,7 +718,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -726,7 +726,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -734,7 +734,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -742,7 +742,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -750,7 +750,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -766,9 +766,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A0516E6-48AB-4411-B864-CA19943C6149}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -776,7 +776,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -784,7 +784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -792,7 +792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -800,7 +800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -808,7 +808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -824,9 +824,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2400FC-7EFF-4C4D-9812-D1FED751AEA5}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -834,7 +834,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -842,7 +842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -858,9 +858,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C1B304-8546-409F-9E78-25DFA4AEFDF8}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -868,7 +868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -876,7 +876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -892,9 +892,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB627A4-118A-44E4-A3D7-B183AF99250D}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
@@ -902,7 +902,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -910,7 +910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -926,12 +926,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1386C902-2D64-462D-B5ED-867AA0AC6E1C}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -939,7 +939,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -955,7 +955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -963,7 +963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -971,7 +971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -987,12 +987,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46100462-1E3D-4C56-9E03-146BD4B8A237}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2000</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3000</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4000</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5000</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6000</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7000</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8000</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9000</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10000</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11000</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12000</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13000</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14000</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15000</v>
       </c>
@@ -1128,17 +1128,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239EF56A-5E90-4B2E-9134-838F7AF45C8D}">
   <dimension ref="A1:D241"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="14.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="14.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>17</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>18</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>19</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>20</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>21</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>22</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>23</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>24</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>25</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>26</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>27</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>28</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>29</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>30</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>31</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>32</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>33</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>34</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>35</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>36</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>37</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>38</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>39</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>40</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>41</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>42</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>43</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>44</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>45</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>46</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>47</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>48</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>49</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>50</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>51</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>52</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>53</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>54</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>55</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>56</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>57</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>58</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>59</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>60</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>61</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>62</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>63</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>64</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>65</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>66</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>67</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>68</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>69</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>70</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>71</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>72</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>73</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>74</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>75</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>76</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>17</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>18</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>1.958</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>19</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>1.8560000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>20</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>1.754</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>21</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>1.6519999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>22</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>23</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>1.448</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>24</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>1.3460000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>25</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>1.244</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>26</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>1.2236</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>27</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>1.2032</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>28</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>1.1828000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>29</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>1.1624000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>30</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>1.1419999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>31</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>1.1215999999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>32</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>1.1012</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>33</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>1.0808</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>34</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>35</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>36</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>37</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>38</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>39</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>40</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>41</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>42</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>43</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>44</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>45</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>46</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>47</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>48</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>49</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>50</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>51</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>52</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>53</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>54</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>55</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>56</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>57</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>58</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>59</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>60</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>61</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>1.0502</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>62</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>63</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>1.0706</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>64</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>1.0808</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>65</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>66</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>1.1012</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>67</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>1.1113999999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>68</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>1.1215999999999999</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>69</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>1.1317999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>70</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>1.1419999999999999</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>71</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>1.244</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>72</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>1.3460000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>73</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>1.448</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>74</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>75</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>1.6519999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>76</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>1.6519999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>17</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>18</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>1.929</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>19</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>1.8280000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>20</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>1.7270000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>21</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>1.6259999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>22</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>1.5249999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>23</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>1.4239999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>24</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>1.323</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>25</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>1.222</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>26</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>1.2018</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>27</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>1.1816</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>28</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>1.1614</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>29</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>1.1412</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>30</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>1.121</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>31</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>1.1008</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>32</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>1.0806</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>33</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>34</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>1.0402</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>35</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>36</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>37</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>38</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>39</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>40</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>41</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>42</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>43</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>44</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>45</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>46</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>47</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>48</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>49</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>50</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>51</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>52</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>53</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>54</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>55</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>56</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>57</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>58</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>59</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>60</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>61</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>1.0301</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>62</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>1.0402</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>63</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>1.0503</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>64</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>65</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>1.0705</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>66</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>1.0806</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>67</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>1.0907</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>68</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>1.1008</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>69</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>1.1109</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>70</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>1.121</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>71</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>1.222</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>72</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>1.323</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>73</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>1.4239999999999999</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>74</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>1.5249999999999999</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>75</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>1.6259999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>76</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>1.6259999999999999</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>17</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>18</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>1.9870000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>19</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>1.8839999999999999</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>20</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>1.7809999999999999</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>21</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>1.6779999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>22</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>1.575</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>23</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>1.472</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>24</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>1.369</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>25</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>26</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>1.2454000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>27</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>1.2248000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>28</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>1.2041999999999999</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>29</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>1.1836</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>30</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>1.163</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>31</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>1.1424000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>32</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>1.1217999999999999</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>33</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>1.1012</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>34</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>1.0806</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>35</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>36</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>37</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>38</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>39</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>40</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>41</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>42</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>43</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>44</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>45</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>46</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>47</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>48</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>49</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>50</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>51</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>52</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>53</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>54</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>55</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>56</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>57</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>58</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>59</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>60</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>61</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>1.0703</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>62</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>1.0806</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>63</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>1.0909</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>64</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>1.1012</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>65</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>1.1114999999999999</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>66</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>1.1217999999999999</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>67</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>1.1321000000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>68</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>1.1424000000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>69</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>1.1527000000000001</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>70</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>1.163</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>71</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>72</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>1.369</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>73</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>1.472</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>74</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>1.575</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>75</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>1.6779999999999999</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>76</v>
       </c>
@@ -4520,12 +4520,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC10BF7E-A413-4CDB-928D-30E579A33E34}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -4565,12 +4565,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1280CA-B471-4644-B06A-FAB6910841EC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4602,9 +4602,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B98AA9D5-08C1-41A0-BDD9-6288A4886FE3}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4636,12 +4636,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{909783C7-0B6F-4BD4-8987-F803B0C3334F}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.54296875" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -4809,12 +4809,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDF60134-A335-4393-9C46-CC6F7FC80A78}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>1.3248175179999999</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>1.2700729930000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4846,7 +4846,7 @@
         <v>1.2165450120000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>1.163017032</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>1.108272506</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>1.0547445259999999</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>0.946472019</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>0.89172749399999995</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>0.83819951299999995</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>0.78345498800000002</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>0.72992700700000002</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>0.68126520700000004</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>0.63260340599999998</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>0.583941606</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>0.55961070599999996</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>0.53527980500000005</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>0.51094890500000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
